--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4323,6 +4323,214 @@
       <c r="K70" t="inlineStr">
         <is>
           <t>登记后随规范升版重建</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>归档-0070</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>27-归档快照与校验.xlsx</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>v3.4</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>证据-0007</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>归档-0071</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0006.docx</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>证据-0006</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>归档-0072</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0007.docx</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>证据-0007</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>归档-0073</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>归档包</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>归档/dcg-tm-v3.4.zip</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>归档包</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>v3.4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>证据-0007</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>由 提交号 8a5c71d 的 git archive 生成，197 份文件 / 1741944 字节；快照记录本身（27）不在包内，属自引用限制</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>在档</t>
         </is>
       </c>
     </row>

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -4377,6 +4377,11 @@
           <t>在档</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>内容基线提交号 8a5c71d；版本标签 tm-v3.4 打在 38e02f7（= 内容基线 + 本快照记录），两者差异仅为本记录与证据-0007；快照记录自身不在包内（自引用限制）</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4539,13 +4539,907 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>归档-0074</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>01-项目画像.docx</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>G0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>归档-0075</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>03-任务书.xlsx</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>G0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>归档-0076</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>06-最终验收结论-0001.docx</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>归档-0077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>08-需求规格说明.docx</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>需求分析</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>G3</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>归档-0078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>10-技术设计文档.docx</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>归档-0079</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>11-API契约.xlsx</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>归档-0080</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>12-数据模型.xlsx</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>G2</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>归档-0081</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>16-代码审查报告.xlsx</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>代码评审</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>归档-0082</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>17-代码审查说明-0001.docx</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>代码评审</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>G4</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>归档-0083</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>18-专项审查报告.xlsx</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>专项评审</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>归档-0084</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>19-专项审查说明-0001.docx</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>专项评审</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>归档-0085</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>21-缺陷说明-0001.docx</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>归档-0086</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>22-集成记录.xlsx</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>记录</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>G7</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>归档-0087</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>23-发布说明-0001.docx</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>归档-0088</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>35-交接与归档说明.docx</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>文档</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>归档-0089</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>模板</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>模板/18-专项审查报告.xlsx</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>模板</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>架构契约</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>G0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>证据-0008</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>类别枚举扩为五类，与附件B 对齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>归档-0090</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>归档包</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>归档/dcg-tm-v3.5.zip</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>归档包</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>v3.5</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>证据-0010</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>由 提交号 3f1aef4 的 git archive 生成，200 份文件（zip 条目 215） / 3514210 字节；快照记录本身不在包内</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"表格,文档"</formula1>
+    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"在档,已迁移,已销毁"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"在档,已迁移,已销毁"</formula1>
+    <dataValidation sqref="D2:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"表格,文档,记录,证据,模板,归档包"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K91"/>
+  <dimension ref="A1:K93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2265,12 +2265,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2493,12 +2493,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2607,12 +2607,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2721,12 +2721,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3177,12 +3177,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3291,12 +3291,12 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3462,12 +3462,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3519,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3633,12 +3633,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3861,12 +3861,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3975,12 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -4089,12 +4089,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -4146,12 +4146,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -4317,12 +4317,12 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>登记后随规范升版重建</t>
+          <t>登记后随规范升版重建；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -5367,12 +5367,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>在档</t>
+          <t>已迁移</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>类别枚举扩为五类，与附件B 对齐</t>
+          <t>类别枚举扩为五类，与附件B 对齐；已迁至 TEAMODEL 仓库 tag tm-v3.5.1</t>
         </is>
       </c>
     </row>
@@ -5430,6 +5430,120 @@
       <c r="K91" t="inlineStr">
         <is>
           <t>由 提交号 3f1aef4 的 git archive 生成，200 份文件（zip 条目 215） / 3514210 字节；快照记录本身不在包内</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>归档-0091</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>24-证据</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0012.docx</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>v3.5.1</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>证据-0012</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>协议与模板外置到 TEAMODEL 仓库的证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>归档-0092</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>24-证据</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0013.docx</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>v3.5.1</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>证据-0013</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>外置后 G0 自检与回归证据</t>
         </is>
       </c>
     </row>

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K93"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5544,6 +5544,63 @@
       <c r="K93" t="inlineStr">
         <is>
           <t>外置后 G0 自检与回归证据</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>归档-0093</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>归档包</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>归档/dcg-tm-v3.5.1.zip</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>归档包</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>v3.5.1</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>集成发布</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>G8</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>证据-0013</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>由 提交号 0436ca2 的 git archive 生成，179 份文件（zip 条目 192） / 6779136 字节；快照记录本身不在包内</t>
         </is>
       </c>
     </row>

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:K95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5601,6 +5601,63 @@
       <c r="K94" t="inlineStr">
         <is>
           <t>由 提交号 0436ca2 的 git archive 生成，179 份文件（zip 条目 192） / 6779136 字节；快照记录本身不在包内</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>归档-0094</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>24-证据</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0014.docx</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>v3.5.1</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>证据-0014</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>README 修订的差异与回归输出</t>
         </is>
       </c>
     </row>

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K95"/>
+  <dimension ref="A1:K96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5658,6 +5658,63 @@
       <c r="K95" t="inlineStr">
         <is>
           <t>README 修订的差异与回归输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>归档-0095</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>24-证据</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0015.docx</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>v3.5.1</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>证据-0015</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>README 定位说明修订的差异与回归输出</t>
         </is>
       </c>
     </row>

--- a/协作/26-归档清单.xlsx
+++ b/协作/26-归档清单.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:K97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5715,6 +5715,63 @@
       <c r="K96" t="inlineStr">
         <is>
           <t>README 定位说明修订的差异与回归输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>归档-0096</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>24-证据</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>24-证据/证据-0016.docx</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>证据</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>v3.5.1</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>测试验证</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>证据-0016</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>长期</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>在档</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>README 精简的差异与回归输出</t>
         </is>
       </c>
     </row>
